--- a/output/yearly_benthic_cover_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_77_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.63003125451721</v>
+        <v>45.44838973266462</v>
       </c>
       <c r="M2" t="n">
-        <v>98.78789218830005</v>
+        <v>98.84689685301558</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04243232322708</v>
+        <v>87.96191919400179</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91903058450904</v>
+        <v>45.84561665019317</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228776724884278</v>
+        <v>2.228625803920369</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701723170680852</v>
+        <v>5.65553482691795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742925574961426</v>
+        <v>0.7428752679734563</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96960227780804</v>
+        <v>33.94493254421397</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17457644822559</v>
+        <v>34.17226232677898</v>
       </c>
       <c r="I3" t="n">
-        <v>6.581543283157984</v>
+        <v>6.574717999362955</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643284843508912</v>
+        <v>4.642970424834101</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95756767677293</v>
+        <v>12.03808080599821</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88716297295293</v>
+        <v>48.88029278433092</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637612342349</v>
+        <v>106.7639902405223</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.2293296488658</v>
+        <v>87.14638116792871</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74402830774527</v>
+        <v>42.66958569464199</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190115834159843</v>
+        <v>2.189763536122405</v>
       </c>
       <c r="E4" t="n">
-        <v>6.518842817444642</v>
+        <v>6.471987881378772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444859147804704</v>
+        <v>0.7444353673728912</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38035748403757</v>
+        <v>33.35300856280961</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24635207990163</v>
+        <v>34.24402689915299</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496138551163691</v>
+        <v>5.490437875011481</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65303696737794</v>
+        <v>4.65272104608057</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7706703511342</v>
+        <v>12.85361883207127</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30248069436615</v>
+        <v>44.29416441774888</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81717935324563</v>
+        <v>99.81736894446215</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.17721225729393</v>
+        <v>86.07126093236259</v>
       </c>
       <c r="C5" t="n">
-        <v>42.54503723540117</v>
+        <v>42.44663592809135</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139158656770042</v>
+        <v>2.137516968551707</v>
       </c>
       <c r="E5" t="n">
-        <v>7.131876961825272</v>
+        <v>7.081484186920521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458071778287708</v>
+        <v>0.7457567954647011</v>
       </c>
       <c r="G5" t="n">
-        <v>32.60370048210252</v>
+        <v>32.55722390989288</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30713018012345</v>
+        <v>34.30481259137625</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588243937214052</v>
+        <v>4.583486508502149</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661294861429817</v>
+        <v>4.660979971654382</v>
       </c>
       <c r="K5" t="n">
-        <v>13.82278774270607</v>
+        <v>13.92873906763741</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47950450658264</v>
+        <v>43.47211284107647</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84732948468988</v>
+        <v>99.84748783680523</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.96629244264764</v>
+        <v>84.81880945190758</v>
       </c>
       <c r="C6" t="n">
-        <v>42.04687956627113</v>
+        <v>41.90612572877787</v>
       </c>
       <c r="D6" t="n">
-        <v>2.080419845298553</v>
+        <v>2.076551248104751</v>
       </c>
       <c r="E6" t="n">
-        <v>7.574257342093087</v>
+        <v>7.517060238934604</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469275848697716</v>
+        <v>0.7468779123676869</v>
       </c>
       <c r="G6" t="n">
-        <v>31.70844074536904</v>
+        <v>31.62863497206359</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35866890400949</v>
+        <v>34.3563839689136</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829280615571618</v>
+        <v>3.825314159225316</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668297405436072</v>
+        <v>4.667986952298043</v>
       </c>
       <c r="K6" t="n">
-        <v>15.03370755735239</v>
+        <v>15.18119054809242</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79196165589831</v>
+        <v>42.78536465344909</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87254877952182</v>
+        <v>99.87268093031938</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.60808142502574</v>
+        <v>83.37812445346803</v>
       </c>
       <c r="C7" t="n">
-        <v>41.28367902994908</v>
+        <v>41.05973300625682</v>
       </c>
       <c r="D7" t="n">
-        <v>2.014669719931154</v>
+        <v>2.006534587188535</v>
       </c>
       <c r="E7" t="n">
-        <v>7.8674005812045</v>
+        <v>7.795573378621321</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478790608055114</v>
+        <v>0.7478309628996386</v>
       </c>
       <c r="G7" t="n">
-        <v>30.70631900589218</v>
+        <v>30.5621881833783</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40243679705352</v>
+        <v>34.40022429338338</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195132130104429</v>
+        <v>3.191829529874107</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674244130034445</v>
+        <v>4.673943518122742</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39191857497426</v>
+        <v>16.62187554653198</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21803348908858</v>
+        <v>42.21213272056607</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89363109401191</v>
+        <v>99.89374127335488</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.57437668123977</v>
+        <v>88.24794589796609</v>
       </c>
       <c r="C8" t="n">
-        <v>43.65428014024043</v>
+        <v>43.3916643686238</v>
       </c>
       <c r="D8" t="n">
-        <v>2.018966331115812</v>
+        <v>2.010784557250905</v>
       </c>
       <c r="E8" t="n">
-        <v>9.747648098770464</v>
+        <v>9.646519980534908</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494740346643224</v>
+        <v>0.7494149172577292</v>
       </c>
       <c r="G8" t="n">
-        <v>31.23129153541034</v>
+        <v>31.07685126580589</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47580559455882</v>
+        <v>34.47308619385555</v>
       </c>
       <c r="I8" t="n">
-        <v>5.666978370068003</v>
+        <v>5.607445750400295</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684212716652014</v>
+        <v>4.683843232860808</v>
       </c>
       <c r="K8" t="n">
-        <v>11.42562331876023</v>
+        <v>11.7520541020339</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73159926313124</v>
+        <v>44.66976173199275</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81150272213189</v>
+        <v>99.81348020265045</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.73547995354876</v>
+        <v>86.27154730630049</v>
       </c>
       <c r="C9" t="n">
-        <v>42.69556360144603</v>
+        <v>42.28598403896164</v>
       </c>
       <c r="D9" t="n">
-        <v>1.936134837575019</v>
+        <v>1.921257221785085</v>
       </c>
       <c r="E9" t="n">
-        <v>10.13624581820472</v>
+        <v>9.997242926257336</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750836726883168</v>
+        <v>0.7507704254573893</v>
       </c>
       <c r="G9" t="n">
-        <v>29.94997520872536</v>
+        <v>29.69319846299196</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53848943662572</v>
+        <v>34.53543957103991</v>
       </c>
       <c r="I9" t="n">
-        <v>4.731068382514976</v>
+        <v>4.681323539660119</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692729543019799</v>
+        <v>4.692315159108683</v>
       </c>
       <c r="K9" t="n">
-        <v>13.26452004645124</v>
+        <v>13.72845269369951</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8825002862675</v>
+        <v>43.82980088538327</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84258393416478</v>
+        <v>99.84423761804442</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.66339589217529</v>
+        <v>84.11593941998588</v>
       </c>
       <c r="C10" t="n">
-        <v>41.35820136091965</v>
+        <v>40.85704497512994</v>
       </c>
       <c r="D10" t="n">
-        <v>1.843527404931076</v>
+        <v>1.824551084999453</v>
       </c>
       <c r="E10" t="n">
-        <v>10.30953255647125</v>
+        <v>10.14522401657365</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520040234400966</v>
+        <v>0.7519328557497457</v>
       </c>
       <c r="G10" t="n">
-        <v>28.51743535767672</v>
+        <v>28.19859665767148</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59218507824443</v>
+        <v>34.5889113644883</v>
       </c>
       <c r="I10" t="n">
-        <v>3.948686324911101</v>
+        <v>3.907143092067324</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700025146500603</v>
+        <v>4.69958034843591</v>
       </c>
       <c r="K10" t="n">
-        <v>15.33660410782471</v>
+        <v>15.88406058001414</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17377596507467</v>
+        <v>43.12885767986536</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86858143381903</v>
+        <v>99.86996323500944</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.39166243286148</v>
+        <v>81.83510831139047</v>
       </c>
       <c r="C11" t="n">
-        <v>39.69919453944298</v>
+        <v>39.18213226918604</v>
       </c>
       <c r="D11" t="n">
-        <v>1.742873661331271</v>
+        <v>1.723235248575627</v>
       </c>
       <c r="E11" t="n">
-        <v>10.29580776939462</v>
+        <v>10.12524739198027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530064800474682</v>
+        <v>0.7529314120832695</v>
       </c>
       <c r="G11" t="n">
-        <v>26.9604275155704</v>
+        <v>26.63275154111726</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63829808218352</v>
+        <v>34.6348449558304</v>
       </c>
       <c r="I11" t="n">
-        <v>3.294958424037536</v>
+        <v>3.260276436283207</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706290500296675</v>
+        <v>4.705821325520435</v>
       </c>
       <c r="K11" t="n">
-        <v>17.60833756713852</v>
+        <v>18.16489168860955</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58278216217095</v>
+        <v>42.54444428964698</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89031426875245</v>
+        <v>99.89146824744256</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.00698818940401</v>
+        <v>79.49185056606053</v>
       </c>
       <c r="C12" t="n">
-        <v>37.82507429733595</v>
+        <v>37.3437240201325</v>
       </c>
       <c r="D12" t="n">
-        <v>1.638176402165831</v>
+        <v>1.620147187468592</v>
       </c>
       <c r="E12" t="n">
-        <v>10.13547906808862</v>
+        <v>9.972863478008497</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538688931372757</v>
+        <v>0.7537901878815819</v>
       </c>
       <c r="G12" t="n">
-        <v>25.34087072873327</v>
+        <v>25.03951653702334</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67796908431467</v>
+        <v>34.67434864255277</v>
       </c>
       <c r="I12" t="n">
-        <v>2.748943430856371</v>
+        <v>2.719995858865851</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711680582107972</v>
+        <v>4.711188674259888</v>
       </c>
       <c r="K12" t="n">
-        <v>19.99301181059598</v>
+        <v>20.50814943393948</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09038726917814</v>
+        <v>42.05756331158684</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90847337711008</v>
+        <v>99.90943676565882</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.59723841423202</v>
+        <v>77.10233255755246</v>
       </c>
       <c r="C13" t="n">
-        <v>35.84044301568304</v>
+        <v>35.37457658449419</v>
       </c>
       <c r="D13" t="n">
-        <v>1.533322729582062</v>
+        <v>1.515951485153245</v>
       </c>
       <c r="E13" t="n">
-        <v>9.86891794527352</v>
+        <v>9.70963154344339</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546114683317857</v>
+        <v>0.7545295794521468</v>
       </c>
       <c r="G13" t="n">
-        <v>23.71889439036991</v>
+        <v>23.42916284114195</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71212754326213</v>
+        <v>34.70836065479875</v>
       </c>
       <c r="I13" t="n">
-        <v>2.293042660338959</v>
+        <v>2.26888658198706</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71632167707366</v>
+        <v>4.715809871575918</v>
       </c>
       <c r="K13" t="n">
-        <v>22.40276158576799</v>
+        <v>22.89766744244755</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68043585880295</v>
+        <v>41.6522005325342</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92364046025398</v>
+        <v>99.92444455947594</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.18133486092017</v>
+        <v>83.95588631811694</v>
       </c>
       <c r="C14" t="n">
-        <v>39.87505521248653</v>
+        <v>39.54499054140913</v>
       </c>
       <c r="D14" t="n">
-        <v>1.535164398603991</v>
+        <v>1.5178030282085</v>
       </c>
       <c r="E14" t="n">
-        <v>12.1356024184517</v>
+        <v>12.04822755170114</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555178297506879</v>
+        <v>0.7554511419272663</v>
       </c>
       <c r="G14" t="n">
-        <v>25.49666436684526</v>
+        <v>25.27180802526855</v>
       </c>
       <c r="H14" t="n">
-        <v>36.50310145688517</v>
+        <v>36.56478195286122</v>
       </c>
       <c r="I14" t="n">
-        <v>3.033297954441561</v>
+        <v>3.076244981104842</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721986435941798</v>
+        <v>4.721569637045414</v>
       </c>
       <c r="K14" t="n">
-        <v>15.81866513907984</v>
+        <v>16.04411368188307</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20529101374476</v>
+        <v>44.30847936603327</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89901136531113</v>
+        <v>99.89758358932548</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.40277947902131</v>
+        <v>83.21923192823533</v>
       </c>
       <c r="C15" t="n">
-        <v>39.54845861459693</v>
+        <v>39.28389160459953</v>
       </c>
       <c r="D15" t="n">
-        <v>1.504142990815389</v>
+        <v>1.490544712211813</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32933685257316</v>
+        <v>12.25954812144885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562818691178096</v>
+        <v>0.7562276523117097</v>
       </c>
       <c r="G15" t="n">
-        <v>24.99869143047981</v>
+        <v>24.81795010289146</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55726009973927</v>
+        <v>36.60236602854198</v>
       </c>
       <c r="I15" t="n">
-        <v>2.530304554309564</v>
+        <v>2.56617248388135</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726761681986309</v>
+        <v>4.726422826948186</v>
       </c>
       <c r="K15" t="n">
-        <v>16.59722052097869</v>
+        <v>16.78076807176467</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77006258791212</v>
+        <v>43.84988907416067</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91574172348774</v>
+        <v>99.91454875052487</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.88786583748337</v>
+        <v>80.80028412478752</v>
       </c>
       <c r="C16" t="n">
-        <v>37.42497068954678</v>
+        <v>37.26173563039955</v>
       </c>
       <c r="D16" t="n">
-        <v>1.407952599781256</v>
+        <v>1.398292871566226</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8926089229765</v>
+        <v>11.8575155573097</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569395998667813</v>
+        <v>0.7568953906556042</v>
       </c>
       <c r="G16" t="n">
-        <v>23.4000176882075</v>
+        <v>23.28193339753232</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58905358183584</v>
+        <v>36.63468540115392</v>
       </c>
       <c r="I16" t="n">
-        <v>2.110420945648134</v>
+        <v>2.140365314972231</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730872499167382</v>
+        <v>4.730596191597526</v>
       </c>
       <c r="K16" t="n">
-        <v>19.11213416251661</v>
+        <v>19.19971587521247</v>
       </c>
       <c r="L16" t="n">
-        <v>43.39260891031689</v>
+        <v>43.4672659253913</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92971376238029</v>
+        <v>99.92871743100332</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.50303716051027</v>
+        <v>82.42711861054083</v>
       </c>
       <c r="C17" t="n">
-        <v>38.60518148483779</v>
+        <v>38.43986612271181</v>
       </c>
       <c r="D17" t="n">
-        <v>1.409153653867538</v>
+        <v>1.399513770455973</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65302281527077</v>
+        <v>12.62090826649552</v>
       </c>
       <c r="F17" t="n">
-        <v>0.75758530725752</v>
+        <v>0.7575562627525002</v>
       </c>
       <c r="G17" t="n">
-        <v>23.81835186182641</v>
+        <v>23.69545102770234</v>
       </c>
       <c r="H17" t="n">
-        <v>37.01863866365765</v>
+        <v>37.05986179067814</v>
       </c>
       <c r="I17" t="n">
-        <v>2.111376688270877</v>
+        <v>2.159100850253231</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7349081703595</v>
+        <v>4.734726642203126</v>
       </c>
       <c r="K17" t="n">
-        <v>17.49696283948976</v>
+        <v>17.57288138945917</v>
       </c>
       <c r="L17" t="n">
-        <v>43.82753643856135</v>
+        <v>43.91534524424118</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92968076288889</v>
+        <v>99.92809275641216</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.01963762027863</v>
+        <v>80.13147831874643</v>
       </c>
       <c r="C18" t="n">
-        <v>36.44796086025048</v>
+        <v>36.47766415370266</v>
       </c>
       <c r="D18" t="n">
-        <v>1.317737140386458</v>
+        <v>1.315314459205776</v>
       </c>
       <c r="E18" t="n">
-        <v>12.12564073121626</v>
+        <v>12.16169300742348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581409768241459</v>
+        <v>0.7581236862787353</v>
       </c>
       <c r="G18" t="n">
-        <v>22.27317566468302</v>
+        <v>22.26985543985379</v>
       </c>
       <c r="H18" t="n">
-        <v>37.04579089418041</v>
+        <v>37.0876203064386</v>
       </c>
       <c r="I18" t="n">
-        <v>1.760771107837422</v>
+        <v>1.800598380303964</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738381105150911</v>
+        <v>4.738273039242094</v>
       </c>
       <c r="K18" t="n">
-        <v>19.98036237972136</v>
+        <v>19.86852168125357</v>
       </c>
       <c r="L18" t="n">
-        <v>43.51302740757622</v>
+        <v>43.59383914142563</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94135064754806</v>
+        <v>99.94002497638185</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.98953884159765</v>
+        <v>79.22822134345417</v>
       </c>
       <c r="C19" t="n">
-        <v>35.68914727718412</v>
+        <v>35.85181272584506</v>
       </c>
       <c r="D19" t="n">
-        <v>1.280525270944252</v>
+        <v>1.28288878570882</v>
       </c>
       <c r="E19" t="n">
-        <v>12.02792515383384</v>
+        <v>12.11211903013363</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586107084413211</v>
+        <v>0.7586025906152605</v>
       </c>
       <c r="G19" t="n">
-        <v>21.64419854967629</v>
+        <v>21.72084979617437</v>
       </c>
       <c r="H19" t="n">
-        <v>37.06874385385178</v>
+        <v>37.11104843896845</v>
       </c>
       <c r="I19" t="n">
-        <v>1.46821837709192</v>
+        <v>1.501446510508249</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741316927758256</v>
+        <v>4.741266191345376</v>
       </c>
       <c r="K19" t="n">
-        <v>21.01046115840233</v>
+        <v>20.77177865654584</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25148125586252</v>
+        <v>43.326391995934</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95108969144897</v>
+        <v>99.9499833783249</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.29140162601617</v>
+        <v>76.74860153188389</v>
       </c>
       <c r="C20" t="n">
-        <v>33.21704168635473</v>
+        <v>33.60337462863242</v>
       </c>
       <c r="D20" t="n">
-        <v>1.182308352316865</v>
+        <v>1.192949027516765</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30940566216555</v>
+        <v>11.47161973469767</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590164633262534</v>
+        <v>0.7590150557880561</v>
       </c>
       <c r="G20" t="n">
-        <v>19.98407786643432</v>
+        <v>20.19806153880062</v>
       </c>
       <c r="H20" t="n">
-        <v>37.0885706553056</v>
+        <v>37.13122634924238</v>
       </c>
       <c r="I20" t="n">
-        <v>1.224169730678494</v>
+        <v>1.251885727163061</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743852895789083</v>
+        <v>4.743844098675349</v>
       </c>
       <c r="K20" t="n">
-        <v>23.70859837398384</v>
+        <v>23.2513984681161</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0335760958533</v>
+        <v>43.10352005573736</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95921615619187</v>
+        <v>99.95829315248588</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.22305253273611</v>
+        <v>82.54941492205886</v>
       </c>
       <c r="C21" t="n">
-        <v>36.85804901886628</v>
+        <v>37.12900725223427</v>
       </c>
       <c r="D21" t="n">
-        <v>1.183177276823727</v>
+        <v>1.193858204816406</v>
       </c>
       <c r="E21" t="n">
-        <v>13.28174147113107</v>
+        <v>13.39266263495313</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595742941195518</v>
+        <v>0.7595935207877252</v>
       </c>
       <c r="G21" t="n">
-        <v>21.66064439412812</v>
+        <v>21.81118986813893</v>
       </c>
       <c r="H21" t="n">
-        <v>38.77770794166196</v>
+        <v>38.75725988131912</v>
       </c>
       <c r="I21" t="n">
-        <v>1.812867816624467</v>
+        <v>1.887391307120255</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747339338247198</v>
+        <v>4.747459504923282</v>
       </c>
       <c r="K21" t="n">
-        <v>17.77694746726391</v>
+        <v>17.45058507794114</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30461896560793</v>
+        <v>45.35754253739683</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93961545173812</v>
+        <v>99.93713486757225</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_77_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.44838973266462</v>
+        <v>45.37555800351373</v>
       </c>
       <c r="M2" t="n">
-        <v>98.84689685301558</v>
+        <v>99.86858590076534</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96191919400179</v>
+        <v>88.03232032187334</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84561665019317</v>
+        <v>45.94523881671237</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228625803920369</v>
+        <v>2.228730914586981</v>
       </c>
       <c r="E3" t="n">
-        <v>5.65553482691795</v>
+        <v>5.716017930356536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428752679734563</v>
+        <v>0.7429103048623271</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94493254421397</v>
+        <v>33.97883007056442</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17226232677898</v>
+        <v>34.17387402366705</v>
       </c>
       <c r="I3" t="n">
-        <v>6.574717999362955</v>
+        <v>6.548767672446472</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642970424834101</v>
+        <v>4.643189405389545</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03808080599821</v>
+        <v>11.96767967812668</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88029278433092</v>
+        <v>48.85201435983318</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639902405223</v>
+        <v>106.7649328546722</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14638116792871</v>
+        <v>87.14538162147822</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66958569464199</v>
+        <v>42.68910158559272</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189763536122405</v>
+        <v>2.186143128167551</v>
       </c>
       <c r="E4" t="n">
-        <v>6.471987881378772</v>
+        <v>6.518246856884842</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444353673728912</v>
+        <v>0.7444643248399171</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35300856280961</v>
+        <v>33.32954434999753</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24402689915299</v>
+        <v>34.24535894263619</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490437875011481</v>
+        <v>5.468721988702718</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65272104608057</v>
+        <v>4.652902030249482</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85361883207127</v>
+        <v>12.85461837852178</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29416441774888</v>
+        <v>44.27436982276198</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81736894446215</v>
+        <v>99.81808978687648</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.07126093236259</v>
+        <v>85.9710791029855</v>
       </c>
       <c r="C5" t="n">
-        <v>42.44663592809135</v>
+        <v>42.36364086205029</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137516968551707</v>
+        <v>2.128830416847666</v>
       </c>
       <c r="E5" t="n">
-        <v>7.081484186920521</v>
+        <v>7.108251357040561</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457567954647011</v>
+        <v>0.7457821048804373</v>
       </c>
       <c r="G5" t="n">
-        <v>32.55722390989288</v>
+        <v>32.45576507674571</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30481259137625</v>
+        <v>34.30597682450011</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583486508502149</v>
+        <v>4.565335167468281</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660979971654382</v>
+        <v>4.661138155502734</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92873906763741</v>
+        <v>14.02892089701448</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47211284107647</v>
+        <v>43.4555292968046</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84748783680523</v>
+        <v>99.84809105586938</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.81880945190758</v>
+        <v>84.49987701024041</v>
       </c>
       <c r="C6" t="n">
-        <v>41.90612572877787</v>
+        <v>41.6015011915843</v>
       </c>
       <c r="D6" t="n">
-        <v>2.076551248104751</v>
+        <v>2.056797841968214</v>
       </c>
       <c r="E6" t="n">
-        <v>7.517060238934604</v>
+        <v>7.502759018137623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468779123676869</v>
+        <v>0.7469030344178402</v>
       </c>
       <c r="G6" t="n">
-        <v>31.62863497206359</v>
+        <v>31.35756941510045</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3563839689136</v>
+        <v>34.35753958322065</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825314159225316</v>
+        <v>3.810164152284134</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667986952298043</v>
+        <v>4.668143965111502</v>
       </c>
       <c r="K6" t="n">
-        <v>15.18119054809242</v>
+        <v>15.50012298975959</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78536465344909</v>
+        <v>42.77156095289308</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87268093031938</v>
+        <v>99.87318513423698</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.37812445346803</v>
+        <v>82.88108837003217</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05973300625682</v>
+        <v>40.57443013501091</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006534587188535</v>
+        <v>1.977951348336044</v>
       </c>
       <c r="E7" t="n">
-        <v>7.795573378621321</v>
+        <v>7.745009954342842</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478309628996386</v>
+        <v>0.7478580377922971</v>
       </c>
       <c r="G7" t="n">
-        <v>30.5621881833783</v>
+        <v>30.15548997551776</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40022429338338</v>
+        <v>34.40146973844566</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191829529874107</v>
+        <v>3.179196579395704</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673943518122742</v>
+        <v>4.674112736201858</v>
       </c>
       <c r="K7" t="n">
-        <v>16.62187554653198</v>
+        <v>17.11891162996782</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21213272056607</v>
+        <v>42.20082034190226</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89374127335488</v>
+        <v>99.89416210688101</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.24794589796609</v>
+        <v>87.86199219157479</v>
       </c>
       <c r="C8" t="n">
-        <v>43.3916643686238</v>
+        <v>42.9487572837201</v>
       </c>
       <c r="D8" t="n">
-        <v>2.010784557250905</v>
+        <v>1.982199723930129</v>
       </c>
       <c r="E8" t="n">
-        <v>9.646519980534908</v>
+        <v>9.62779578061803</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494149172577292</v>
+        <v>0.7494643370767913</v>
       </c>
       <c r="G8" t="n">
-        <v>31.07685126580589</v>
+        <v>30.6815456424333</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47308619385555</v>
+        <v>34.4753595055324</v>
       </c>
       <c r="I8" t="n">
-        <v>5.607445750400295</v>
+        <v>5.661475095254207</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683843232860808</v>
+        <v>4.684152106729947</v>
       </c>
       <c r="K8" t="n">
-        <v>11.7520541020339</v>
+        <v>12.1380078084252</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66976173199275</v>
+        <v>44.72492353904155</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81348020265045</v>
+        <v>99.81168863118685</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.27154730630049</v>
+        <v>85.87194124228758</v>
       </c>
       <c r="C9" t="n">
-        <v>42.28598403896164</v>
+        <v>41.83727052022298</v>
       </c>
       <c r="D9" t="n">
-        <v>1.921257221785085</v>
+        <v>1.892391929862803</v>
       </c>
       <c r="E9" t="n">
-        <v>9.997242926257336</v>
+        <v>9.979346582169246</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507704254573893</v>
+        <v>0.7508394009566531</v>
       </c>
       <c r="G9" t="n">
-        <v>29.69319846299196</v>
+        <v>29.29145265661668</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53543957103991</v>
+        <v>34.53861244400604</v>
       </c>
       <c r="I9" t="n">
-        <v>4.681323539660119</v>
+        <v>4.726551972697056</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692315159108683</v>
+        <v>4.692746255979083</v>
       </c>
       <c r="K9" t="n">
-        <v>13.72845269369951</v>
+        <v>14.12805875771243</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82980088538327</v>
+        <v>43.87740752497418</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84423761804442</v>
+        <v>99.8427368029096</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.11593941998588</v>
+        <v>83.64328769645837</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85704497512994</v>
+        <v>40.34184257553968</v>
       </c>
       <c r="D10" t="n">
-        <v>1.824551084999453</v>
+        <v>1.792748266876136</v>
       </c>
       <c r="E10" t="n">
-        <v>10.14522401657365</v>
+        <v>10.11138293422789</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519328557497457</v>
+        <v>0.7520198306759471</v>
       </c>
       <c r="G10" t="n">
-        <v>28.19859665767148</v>
+        <v>27.74911484020176</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5889113644883</v>
+        <v>34.59291221109356</v>
       </c>
       <c r="I10" t="n">
-        <v>3.907143092067324</v>
+        <v>3.944985671658418</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69958034843591</v>
+        <v>4.70012394172467</v>
       </c>
       <c r="K10" t="n">
-        <v>15.88406058001414</v>
+        <v>16.35671230354162</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12885767986536</v>
+        <v>43.170152010566</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86996323500944</v>
+        <v>99.8687068896473</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.83510831139047</v>
+        <v>81.25875842921025</v>
       </c>
       <c r="C11" t="n">
-        <v>39.18213226918604</v>
+        <v>38.56865128135284</v>
       </c>
       <c r="D11" t="n">
-        <v>1.723235248575627</v>
+        <v>1.687217521556387</v>
       </c>
       <c r="E11" t="n">
-        <v>10.12524739198027</v>
+        <v>10.06482746330468</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529314120832695</v>
+        <v>0.7530353498104996</v>
       </c>
       <c r="G11" t="n">
-        <v>26.63275154111726</v>
+        <v>26.11565362026568</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6348449558304</v>
+        <v>34.63962609128298</v>
       </c>
       <c r="I11" t="n">
-        <v>3.260276436283207</v>
+        <v>3.291927446674404</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705821325520435</v>
+        <v>4.706470936315623</v>
       </c>
       <c r="K11" t="n">
-        <v>18.16489168860955</v>
+        <v>18.74124157078975</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54444428964698</v>
+        <v>42.58052421253358</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89146824744256</v>
+        <v>99.89041706467617</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.49185056606053</v>
+        <v>78.74759549056255</v>
       </c>
       <c r="C12" t="n">
-        <v>37.3437240201325</v>
+        <v>36.56678316166098</v>
       </c>
       <c r="D12" t="n">
-        <v>1.620147187468592</v>
+        <v>1.577162599629591</v>
       </c>
       <c r="E12" t="n">
-        <v>9.972863478008497</v>
+        <v>9.866056032506616</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537901878815819</v>
+        <v>0.7539107979335684</v>
       </c>
       <c r="G12" t="n">
-        <v>25.03951653702334</v>
+        <v>24.41216477930443</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67434864255277</v>
+        <v>34.67989670494414</v>
       </c>
       <c r="I12" t="n">
-        <v>2.719995858865851</v>
+        <v>2.746462089159405</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711188674259888</v>
+        <v>4.711942487084803</v>
       </c>
       <c r="K12" t="n">
-        <v>20.50814943393948</v>
+        <v>21.25240450943745</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05756331158684</v>
+        <v>42.08936989982728</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90943676565882</v>
+        <v>99.90855757092569</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.10233255755246</v>
+        <v>76.27957460408338</v>
       </c>
       <c r="C13" t="n">
-        <v>35.37457658449419</v>
+        <v>34.52272639083381</v>
       </c>
       <c r="D13" t="n">
-        <v>1.515951485153245</v>
+        <v>1.470072611272176</v>
       </c>
       <c r="E13" t="n">
-        <v>9.70963154344339</v>
+        <v>9.577981733427981</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545295794521468</v>
+        <v>0.754665572719547</v>
       </c>
       <c r="G13" t="n">
-        <v>23.42916284114195</v>
+        <v>22.75456876313653</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70836065479875</v>
+        <v>34.71461634509916</v>
       </c>
       <c r="I13" t="n">
-        <v>2.26888658198706</v>
+        <v>2.291009748930802</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715809871575918</v>
+        <v>4.71665982949717</v>
       </c>
       <c r="K13" t="n">
-        <v>22.89766744244755</v>
+        <v>23.72042539591665</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6522005325342</v>
+        <v>41.68055759966178</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92444455947594</v>
+        <v>99.92370938641224</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.95588631811694</v>
+        <v>83.13596008796111</v>
       </c>
       <c r="C14" t="n">
-        <v>39.54499054140913</v>
+        <v>38.89570988224119</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5178030282085</v>
+        <v>1.471712272559409</v>
       </c>
       <c r="E14" t="n">
-        <v>12.04822755170114</v>
+        <v>11.99211115805957</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554511419272663</v>
+        <v>0.7555072970771797</v>
       </c>
       <c r="G14" t="n">
-        <v>25.27180802526855</v>
+        <v>24.71976190261093</v>
       </c>
       <c r="H14" t="n">
-        <v>36.56478195286122</v>
+        <v>36.69314925218995</v>
       </c>
       <c r="I14" t="n">
-        <v>3.076244981104842</v>
+        <v>2.781797598731699</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721569637045414</v>
+        <v>4.721920606732374</v>
       </c>
       <c r="K14" t="n">
-        <v>16.04411368188307</v>
+        <v>16.86403991203888</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30847936603327</v>
+        <v>44.14762692746445</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89758358932548</v>
+        <v>99.90737672174453</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.21923192823533</v>
+        <v>82.31241120877664</v>
       </c>
       <c r="C15" t="n">
-        <v>39.28389160459953</v>
+        <v>38.47955995097558</v>
       </c>
       <c r="D15" t="n">
-        <v>1.490544712211813</v>
+        <v>1.438737130873479</v>
       </c>
       <c r="E15" t="n">
-        <v>12.25954812144885</v>
+        <v>12.13250566472684</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562276523117097</v>
+        <v>0.7562172086554733</v>
       </c>
       <c r="G15" t="n">
-        <v>24.81795010289146</v>
+        <v>24.18825722176203</v>
       </c>
       <c r="H15" t="n">
-        <v>36.60236602854198</v>
+        <v>36.74999350224287</v>
       </c>
       <c r="I15" t="n">
-        <v>2.56617248388135</v>
+        <v>2.32034292641924</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726422826948186</v>
+        <v>4.726357554096708</v>
       </c>
       <c r="K15" t="n">
-        <v>16.78076807176467</v>
+        <v>17.68758879122336</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84988907416067</v>
+        <v>43.75557910228073</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91454875052487</v>
+        <v>99.92272784447968</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.80028412478752</v>
+        <v>79.67575103443507</v>
       </c>
       <c r="C16" t="n">
-        <v>37.26173563039955</v>
+        <v>36.20132690256781</v>
       </c>
       <c r="D16" t="n">
-        <v>1.398292871566226</v>
+        <v>1.339356860168206</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8575155573097</v>
+        <v>11.61698778697159</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568953906556042</v>
+        <v>0.7568294484155625</v>
       </c>
       <c r="G16" t="n">
-        <v>23.28193339753232</v>
+        <v>22.51746170324499</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63468540115392</v>
+        <v>36.77974660353118</v>
       </c>
       <c r="I16" t="n">
-        <v>2.140365314972231</v>
+        <v>1.935184579506279</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730596191597526</v>
+        <v>4.730184052597266</v>
       </c>
       <c r="K16" t="n">
-        <v>19.19971587521247</v>
+        <v>20.32424896556493</v>
       </c>
       <c r="L16" t="n">
-        <v>43.4672659253913</v>
+        <v>43.40997016168894</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92871743100332</v>
+        <v>99.93554602982168</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.42711861054083</v>
+        <v>81.54769846950768</v>
       </c>
       <c r="C17" t="n">
-        <v>38.43986612271181</v>
+        <v>37.56595841516709</v>
       </c>
       <c r="D17" t="n">
-        <v>1.399513770455973</v>
+        <v>1.340397377177119</v>
       </c>
       <c r="E17" t="n">
-        <v>12.62090826649552</v>
+        <v>12.45257432199991</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575562627525002</v>
+        <v>0.7574174126373038</v>
       </c>
       <c r="G17" t="n">
-        <v>23.69545102770234</v>
+        <v>23.04475347364341</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05986179067814</v>
+        <v>37.31811843068375</v>
       </c>
       <c r="I17" t="n">
-        <v>2.159100850253231</v>
+        <v>1.900578624383038</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734726642203126</v>
+        <v>4.733858828983148</v>
       </c>
       <c r="K17" t="n">
-        <v>17.57288138945917</v>
+        <v>18.45230153049233</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91534524424118</v>
+        <v>43.91843661258518</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92809275641216</v>
+        <v>99.93669655824461</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.13147831874643</v>
+        <v>78.96161793688891</v>
       </c>
       <c r="C18" t="n">
-        <v>36.47766415370266</v>
+        <v>35.2730313062255</v>
       </c>
       <c r="D18" t="n">
-        <v>1.315314459205776</v>
+        <v>1.247132687962412</v>
       </c>
       <c r="E18" t="n">
-        <v>12.16169300742348</v>
+        <v>11.85027155148376</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581236862787353</v>
+        <v>0.7579241618158175</v>
       </c>
       <c r="G18" t="n">
-        <v>22.26985543985379</v>
+        <v>21.4413022827173</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0876203064386</v>
+        <v>37.34308607143626</v>
       </c>
       <c r="I18" t="n">
-        <v>1.800598380303964</v>
+        <v>1.584875170124508</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738273039242094</v>
+        <v>4.737026011348859</v>
       </c>
       <c r="K18" t="n">
-        <v>19.86852168125357</v>
+        <v>21.03838206311111</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59383914142563</v>
+        <v>43.63579277998609</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94002497638185</v>
+        <v>99.94720614932268</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.22822134345417</v>
+        <v>77.85597367236615</v>
       </c>
       <c r="C19" t="n">
-        <v>35.85181272584506</v>
+        <v>34.40180018450335</v>
       </c>
       <c r="D19" t="n">
-        <v>1.28288878570882</v>
+        <v>1.207506950315178</v>
       </c>
       <c r="E19" t="n">
-        <v>12.11211903013363</v>
+        <v>11.69549631243685</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586025906152605</v>
+        <v>0.7583559050891168</v>
       </c>
       <c r="G19" t="n">
-        <v>21.72084979617437</v>
+        <v>20.76003762878691</v>
       </c>
       <c r="H19" t="n">
-        <v>37.11104843896845</v>
+        <v>37.36435815514574</v>
       </c>
       <c r="I19" t="n">
-        <v>1.501446510508249</v>
+        <v>1.330494313785367</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741266191345376</v>
+        <v>4.739724406806979</v>
       </c>
       <c r="K19" t="n">
-        <v>20.77177865654584</v>
+        <v>22.14402632763387</v>
       </c>
       <c r="L19" t="n">
-        <v>43.326391995934</v>
+        <v>43.40984892640868</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9499833783249</v>
+        <v>99.9556754385459</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.74860153188389</v>
+        <v>74.9488027355964</v>
       </c>
       <c r="C20" t="n">
-        <v>33.60337462863242</v>
+        <v>31.69901673677295</v>
       </c>
       <c r="D20" t="n">
-        <v>1.192949027516765</v>
+        <v>1.103769830417535</v>
       </c>
       <c r="E20" t="n">
-        <v>11.47161973469767</v>
+        <v>10.87561635297293</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590150557880561</v>
+        <v>0.7587300441949885</v>
       </c>
       <c r="G20" t="n">
-        <v>20.19806153880062</v>
+        <v>18.97653939549316</v>
       </c>
       <c r="H20" t="n">
-        <v>37.13122634924238</v>
+        <v>37.38279206916661</v>
       </c>
       <c r="I20" t="n">
-        <v>1.251885727163061</v>
+        <v>1.109292267132503</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743844098675349</v>
+        <v>4.742062776218678</v>
       </c>
       <c r="K20" t="n">
-        <v>23.2513984681161</v>
+        <v>25.0511972644036</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10352005573736</v>
+        <v>43.21282782344052</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95829315248588</v>
+        <v>99.96304182461708</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.54941492205886</v>
+        <v>81.18213489435433</v>
       </c>
       <c r="C21" t="n">
-        <v>37.12900725223427</v>
+        <v>35.67125647237199</v>
       </c>
       <c r="D21" t="n">
-        <v>1.193858204816406</v>
+        <v>1.104441807966636</v>
       </c>
       <c r="E21" t="n">
-        <v>13.39266263495313</v>
+        <v>12.98530193563792</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595935207877252</v>
+        <v>0.7591919607481291</v>
       </c>
       <c r="G21" t="n">
-        <v>21.81118986813893</v>
+        <v>20.84403750898927</v>
       </c>
       <c r="H21" t="n">
-        <v>38.75725988131912</v>
+        <v>39.26149595058547</v>
       </c>
       <c r="I21" t="n">
-        <v>1.887391307120255</v>
+        <v>1.482715975751103</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747459504923282</v>
+        <v>4.744949754675807</v>
       </c>
       <c r="K21" t="n">
-        <v>17.45058507794114</v>
+        <v>18.81786510564567</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35754253739683</v>
+        <v>45.46148462717707</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93713486757225</v>
+        <v>99.95060620519473</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_77_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.37555800351373</v>
+        <v>43.92661501481332</v>
       </c>
       <c r="M2" t="n">
-        <v>99.86858590076534</v>
+        <v>95.47944356147408</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03232032187334</v>
+        <v>81.37009599603492</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94523881671237</v>
+        <v>43.12565155159049</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228730914586981</v>
+        <v>2.174671612172248</v>
       </c>
       <c r="E3" t="n">
-        <v>5.716017930356536</v>
+        <v>4.13664539963481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429103048623271</v>
+        <v>0.7375575062607308</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97883007056442</v>
+        <v>32.71068549975757</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17387402366705</v>
+        <v>33.92764528799361</v>
       </c>
       <c r="I3" t="n">
-        <v>6.548767672446472</v>
+        <v>3.073156276086378</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643189405389545</v>
+        <v>4.609734414129568</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96767967812668</v>
+        <v>18.62990400396508</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85201435983318</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7649328546722</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14538162147822</v>
+        <v>88.07904991859796</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68910158559272</v>
+        <v>42.56963600169158</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186143128167551</v>
+        <v>2.18023871498292</v>
       </c>
       <c r="E4" t="n">
-        <v>6.518246856884842</v>
+        <v>6.401215039168983</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444643248399171</v>
+        <v>0.7394456343087328</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32954434999753</v>
+        <v>33.35771377507358</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24535894263619</v>
+        <v>34.0144991782017</v>
       </c>
       <c r="I4" t="n">
-        <v>5.468721988702718</v>
+        <v>6.764402362432453</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652902030249482</v>
+        <v>4.62153521442958</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85461837852178</v>
+        <v>11.92095008140206</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27436982276198</v>
+        <v>45.28450958739723</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81808978687648</v>
+        <v>99.77509567049086</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.9710791029855</v>
+        <v>86.55905890715962</v>
       </c>
       <c r="C5" t="n">
-        <v>42.36364086205029</v>
+        <v>42.09812248021149</v>
       </c>
       <c r="D5" t="n">
-        <v>2.128830416847666</v>
+        <v>2.105792051903161</v>
       </c>
       <c r="E5" t="n">
-        <v>7.108251357040561</v>
+        <v>7.124182676359245</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457821048804373</v>
+        <v>0.7410542949435434</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45576507674571</v>
+        <v>32.21867773215872</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30597682450011</v>
+        <v>34.08849756740299</v>
       </c>
       <c r="I5" t="n">
-        <v>4.565335167468281</v>
+        <v>5.649265240994811</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661138155502734</v>
+        <v>4.631589343397146</v>
       </c>
       <c r="K5" t="n">
-        <v>14.02892089701448</v>
+        <v>13.44094109284041</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4555292968046</v>
+        <v>44.27303636132499</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84809105586938</v>
+        <v>99.81209993437687</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.49987701024041</v>
+        <v>84.63042601528505</v>
       </c>
       <c r="C6" t="n">
-        <v>41.6015011915843</v>
+        <v>41.04569403585053</v>
       </c>
       <c r="D6" t="n">
-        <v>2.056797841968214</v>
+        <v>2.011538019707504</v>
       </c>
       <c r="E6" t="n">
-        <v>7.502759018137623</v>
+        <v>7.591386126407092</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469030344178402</v>
+        <v>0.7424309305393045</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35756941510045</v>
+        <v>30.77658838362885</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35753958322065</v>
+        <v>34.151822804808</v>
       </c>
       <c r="I6" t="n">
-        <v>3.810164152284134</v>
+        <v>4.716466434323655</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668143965111502</v>
+        <v>4.640193315870653</v>
       </c>
       <c r="K6" t="n">
-        <v>15.50012298975959</v>
+        <v>15.36957398471494</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77156095289308</v>
+        <v>43.42780794496247</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87318513423698</v>
+        <v>99.84307596552794</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.88108837003217</v>
+        <v>82.45816673815646</v>
       </c>
       <c r="C7" t="n">
-        <v>40.57443013501091</v>
+        <v>39.6047489656991</v>
       </c>
       <c r="D7" t="n">
-        <v>1.977951348336044</v>
+        <v>1.906354064334038</v>
       </c>
       <c r="E7" t="n">
-        <v>7.745009954342842</v>
+        <v>7.850537392458772</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478580377922971</v>
+        <v>0.7436124127932843</v>
       </c>
       <c r="G7" t="n">
-        <v>30.15548997551776</v>
+        <v>29.16727090248978</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40146973844566</v>
+        <v>34.20617098849107</v>
       </c>
       <c r="I7" t="n">
-        <v>3.179196579395704</v>
+        <v>3.936643397631494</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674112736201858</v>
+        <v>4.647577579958027</v>
       </c>
       <c r="K7" t="n">
-        <v>17.11891162996782</v>
+        <v>17.54183326184354</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20082034190226</v>
+        <v>42.72240481594837</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89416210688101</v>
+        <v>99.868987043491</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.86199219157479</v>
+        <v>80.10718355908331</v>
       </c>
       <c r="C8" t="n">
-        <v>42.9487572837201</v>
+        <v>37.86354762045151</v>
       </c>
       <c r="D8" t="n">
-        <v>1.982199723930129</v>
+        <v>1.793660509435301</v>
       </c>
       <c r="E8" t="n">
-        <v>9.62779578061803</v>
+        <v>7.933958606837664</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494643370767913</v>
+        <v>0.7446288767569164</v>
       </c>
       <c r="G8" t="n">
-        <v>30.6815456424333</v>
+        <v>27.4430563370049</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4753595055324</v>
+        <v>34.25292833081814</v>
       </c>
       <c r="I8" t="n">
-        <v>5.661475095254207</v>
+        <v>3.285020418499644</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684152106729947</v>
+        <v>4.653930479730727</v>
       </c>
       <c r="K8" t="n">
-        <v>12.1380078084252</v>
+        <v>19.89281644091671</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72492353904155</v>
+        <v>42.134284733142</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81168863118685</v>
+        <v>99.89064879451023</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.87194124228758</v>
+        <v>77.68867826434153</v>
       </c>
       <c r="C9" t="n">
-        <v>41.83727052022298</v>
+        <v>35.95305187119575</v>
       </c>
       <c r="D9" t="n">
-        <v>1.892391929862803</v>
+        <v>1.678928229258013</v>
       </c>
       <c r="E9" t="n">
-        <v>9.979346582169246</v>
+        <v>7.883248834849803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508394009566531</v>
+        <v>0.7455045218570124</v>
       </c>
       <c r="G9" t="n">
-        <v>29.29145265661668</v>
+        <v>25.68764921730997</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53861244400604</v>
+        <v>34.29320800542256</v>
       </c>
       <c r="I9" t="n">
-        <v>4.726551972697056</v>
+        <v>2.740736194037832</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692746255979083</v>
+        <v>4.659403261606328</v>
       </c>
       <c r="K9" t="n">
-        <v>14.12805875771243</v>
+        <v>22.31132173565848</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87740752497418</v>
+        <v>41.64437582596524</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8427368029096</v>
+        <v>99.90874943281946</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.64328769645837</v>
+        <v>83.84144398823287</v>
       </c>
       <c r="C10" t="n">
-        <v>40.34184257553968</v>
+        <v>40.11669958147291</v>
       </c>
       <c r="D10" t="n">
-        <v>1.792748266876136</v>
+        <v>1.680835546851432</v>
       </c>
       <c r="E10" t="n">
-        <v>10.11138293422789</v>
+        <v>10.19334644151799</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520198306759471</v>
+        <v>0.7463514394713167</v>
       </c>
       <c r="G10" t="n">
-        <v>27.74911484020176</v>
+        <v>27.54174004152579</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59291221109356</v>
+        <v>36.15707502697174</v>
       </c>
       <c r="I10" t="n">
-        <v>3.944985671658418</v>
+        <v>2.857398995198863</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70012394172467</v>
+        <v>4.664696496695729</v>
       </c>
       <c r="K10" t="n">
-        <v>16.35671230354162</v>
+        <v>16.15855601176712</v>
       </c>
       <c r="L10" t="n">
-        <v>43.170152010566</v>
+        <v>43.62960585410622</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8687068896473</v>
+        <v>99.90486144734626</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.25875842921025</v>
+        <v>83.09325406282638</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56865128135284</v>
+        <v>39.6958468690388</v>
       </c>
       <c r="D11" t="n">
-        <v>1.687217521556387</v>
+        <v>1.64043756448884</v>
       </c>
       <c r="E11" t="n">
-        <v>10.06482746330468</v>
+        <v>10.41126814206814</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530353498104996</v>
+        <v>0.7470821826261937</v>
       </c>
       <c r="G11" t="n">
-        <v>26.11565362026568</v>
+        <v>26.93592467615166</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63962609128298</v>
+        <v>36.24861156624493</v>
       </c>
       <c r="I11" t="n">
-        <v>3.291927446674404</v>
+        <v>2.440666289832905</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706470936315623</v>
+        <v>4.669263641413711</v>
       </c>
       <c r="K11" t="n">
-        <v>18.74124157078975</v>
+        <v>16.90674593717362</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58052421253358</v>
+        <v>43.31613122705333</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89041706467617</v>
+        <v>99.91872403326576</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.74759549056255</v>
+        <v>80.69448117470088</v>
       </c>
       <c r="C12" t="n">
-        <v>36.56678316166098</v>
+        <v>37.67492110635276</v>
       </c>
       <c r="D12" t="n">
-        <v>1.577162599629591</v>
+        <v>1.540801683997058</v>
       </c>
       <c r="E12" t="n">
-        <v>9.866056032506616</v>
+        <v>10.11818145505013</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539107979335684</v>
+        <v>0.7477103790758018</v>
       </c>
       <c r="G12" t="n">
-        <v>24.41216477930443</v>
+        <v>25.29990717078264</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67989670494414</v>
+        <v>36.27909181275422</v>
       </c>
       <c r="I12" t="n">
-        <v>2.746462089159405</v>
+        <v>2.035598803817273</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711942487084803</v>
+        <v>4.673189869223761</v>
       </c>
       <c r="K12" t="n">
-        <v>21.25240450943745</v>
+        <v>19.30551882529915</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08936989982728</v>
+        <v>42.95176378251939</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90855757092569</v>
+        <v>99.93220371417129</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.27957460408338</v>
+        <v>82.05914975351209</v>
       </c>
       <c r="C13" t="n">
-        <v>34.52272639083381</v>
+        <v>38.77753988783847</v>
       </c>
       <c r="D13" t="n">
-        <v>1.470072611272176</v>
+        <v>1.541984443163764</v>
       </c>
       <c r="E13" t="n">
-        <v>9.577981733427981</v>
+        <v>10.81930587891883</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754665572719547</v>
+        <v>0.7482843408737918</v>
       </c>
       <c r="G13" t="n">
-        <v>22.75456876313653</v>
+        <v>25.69773186600209</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71461634509916</v>
+        <v>36.6853444136627</v>
       </c>
       <c r="I13" t="n">
-        <v>2.291009748930802</v>
+        <v>1.889721680429713</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71665982949717</v>
+        <v>4.676777130461198</v>
       </c>
       <c r="K13" t="n">
-        <v>23.72042539591665</v>
+        <v>17.94085024648791</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68055759966178</v>
+        <v>43.21866745920946</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92370938641224</v>
+        <v>99.93705759353584</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.13596008796111</v>
+        <v>79.69461040783364</v>
       </c>
       <c r="C14" t="n">
-        <v>38.89570988224119</v>
+        <v>36.70522852778416</v>
       </c>
       <c r="D14" t="n">
-        <v>1.471712272559409</v>
+        <v>1.447136875107377</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99211115805957</v>
+        <v>10.41644397114173</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555072970771797</v>
+        <v>0.7487775364812579</v>
       </c>
       <c r="G14" t="n">
-        <v>24.71976190261093</v>
+        <v>24.1170626297713</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69314925218995</v>
+        <v>36.70952379272344</v>
       </c>
       <c r="I14" t="n">
-        <v>2.781797598731699</v>
+        <v>1.575805999600669</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721920606732374</v>
+        <v>4.679859603007861</v>
       </c>
       <c r="K14" t="n">
-        <v>16.86403991203888</v>
+        <v>20.30538959216636</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14762692746445</v>
+        <v>42.93688961114866</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90737672174453</v>
+        <v>99.94750773109919</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.31241120877664</v>
+        <v>78.67215944376876</v>
       </c>
       <c r="C15" t="n">
-        <v>38.47955995097558</v>
+        <v>35.88257400731509</v>
       </c>
       <c r="D15" t="n">
-        <v>1.438737130873479</v>
+        <v>1.40424981688657</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13250566472684</v>
+        <v>10.33990518580044</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562172086554733</v>
+        <v>0.7492054085479205</v>
       </c>
       <c r="G15" t="n">
-        <v>24.18825722176203</v>
+        <v>23.40971788520431</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74999350224287</v>
+        <v>36.73788431076181</v>
       </c>
       <c r="I15" t="n">
-        <v>2.32034292641924</v>
+        <v>1.348663033143201</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726357554096708</v>
+        <v>4.682533803424502</v>
       </c>
       <c r="K15" t="n">
-        <v>17.68758879122336</v>
+        <v>21.32784055623124</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75557910228073</v>
+        <v>42.74465567611564</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92272784447968</v>
+        <v>99.95507023966196</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.67575103443507</v>
+        <v>75.94046609165608</v>
       </c>
       <c r="C16" t="n">
-        <v>36.20132690256781</v>
+        <v>33.35869925448535</v>
       </c>
       <c r="D16" t="n">
-        <v>1.339356860168206</v>
+        <v>1.29576934925443</v>
       </c>
       <c r="E16" t="n">
-        <v>11.61698778697159</v>
+        <v>9.728538298610225</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568294484155625</v>
+        <v>0.7495751881041913</v>
       </c>
       <c r="G16" t="n">
-        <v>22.51746170324499</v>
+        <v>21.60128101536452</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77974660353118</v>
+        <v>36.7560167460109</v>
       </c>
       <c r="I16" t="n">
-        <v>1.935184579506279</v>
+        <v>1.124440568660622</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730184052597266</v>
+        <v>4.684844925651195</v>
       </c>
       <c r="K16" t="n">
-        <v>20.32424896556493</v>
+        <v>24.05953390834391</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40997016168894</v>
+        <v>42.54430397513899</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93554602982168</v>
+        <v>99.96253713796825</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.54769846950768</v>
+        <v>81.88167922101542</v>
       </c>
       <c r="C17" t="n">
-        <v>37.56595841516709</v>
+        <v>37.28577308407119</v>
       </c>
       <c r="D17" t="n">
-        <v>1.340397377177119</v>
+        <v>1.296435859022228</v>
       </c>
       <c r="E17" t="n">
-        <v>12.45257432199991</v>
+        <v>11.79514724782399</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574174126373038</v>
+        <v>0.7499607499210829</v>
       </c>
       <c r="G17" t="n">
-        <v>23.04475347364341</v>
+        <v>23.46340805104652</v>
       </c>
       <c r="H17" t="n">
-        <v>37.31811843068375</v>
+        <v>38.62593898027411</v>
       </c>
       <c r="I17" t="n">
-        <v>1.900578624383038</v>
+        <v>1.263533645920713</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733858828983148</v>
+        <v>4.687254687006767</v>
       </c>
       <c r="K17" t="n">
-        <v>18.45230153049233</v>
+        <v>18.11832077898461</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91843661258518</v>
+        <v>44.5538100018946</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93669655824461</v>
+        <v>99.9579038649504</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.96161793688891</v>
+        <v>83.64016607390818</v>
       </c>
       <c r="C18" t="n">
-        <v>35.2730313062255</v>
+        <v>38.05036707376961</v>
       </c>
       <c r="D18" t="n">
-        <v>1.247132687962412</v>
+        <v>1.297575173709879</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85027155148376</v>
+        <v>12.42539874639172</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579241618158175</v>
+        <v>0.7506198193934365</v>
       </c>
       <c r="G18" t="n">
-        <v>21.4413022827173</v>
+        <v>23.61021219804552</v>
       </c>
       <c r="H18" t="n">
-        <v>37.34308607143626</v>
+        <v>38.65988365967976</v>
       </c>
       <c r="I18" t="n">
-        <v>1.584875170124508</v>
+        <v>2.205102605478882</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737026011348859</v>
+        <v>4.691373871208977</v>
       </c>
       <c r="K18" t="n">
-        <v>21.03838206311111</v>
+        <v>16.35983392609181</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63579277998609</v>
+        <v>45.51636011843352</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94720614932268</v>
+        <v>99.92656111829494</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.85597367236615</v>
+        <v>80.46506637117245</v>
       </c>
       <c r="C19" t="n">
-        <v>34.40180018450335</v>
+        <v>35.21497048556578</v>
       </c>
       <c r="D19" t="n">
-        <v>1.207506950315178</v>
+        <v>1.188123897873534</v>
       </c>
       <c r="E19" t="n">
-        <v>11.69549631243685</v>
+        <v>11.6838061738528</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583559050891168</v>
+        <v>0.7511916530081015</v>
       </c>
       <c r="G19" t="n">
-        <v>20.76003762878691</v>
+        <v>21.61867606187351</v>
       </c>
       <c r="H19" t="n">
-        <v>37.36435815514574</v>
+        <v>38.68933534806378</v>
       </c>
       <c r="I19" t="n">
-        <v>1.330494313785367</v>
+        <v>1.838985405200094</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739724406806979</v>
+        <v>4.694947831300634</v>
       </c>
       <c r="K19" t="n">
-        <v>22.14402632763387</v>
+        <v>19.53493362882754</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40984892640868</v>
+        <v>45.18884303545447</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9556754385459</v>
+        <v>99.9387471498478</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.9488027355964</v>
+        <v>77.19058434833582</v>
       </c>
       <c r="C20" t="n">
-        <v>31.69901673677295</v>
+        <v>32.22273040338243</v>
       </c>
       <c r="D20" t="n">
-        <v>1.103769830417535</v>
+        <v>1.076037444815295</v>
       </c>
       <c r="E20" t="n">
-        <v>10.87561635297293</v>
+        <v>10.83715104107034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587300441949885</v>
+        <v>0.7516891033203257</v>
       </c>
       <c r="G20" t="n">
-        <v>18.97653939549316</v>
+        <v>19.57919118666196</v>
       </c>
       <c r="H20" t="n">
-        <v>37.38279206916661</v>
+        <v>38.71495600275499</v>
       </c>
       <c r="I20" t="n">
-        <v>1.109292267132503</v>
+        <v>1.533502673960885</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742062776218678</v>
+        <v>4.698056895752035</v>
       </c>
       <c r="K20" t="n">
-        <v>25.0511972644036</v>
+        <v>22.80941565166419</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21282782344052</v>
+        <v>44.91677101703115</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96304182461708</v>
+        <v>99.94891707207776</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.18213489435433</v>
+        <v>73.91634776242522</v>
       </c>
       <c r="C21" t="n">
-        <v>35.67125647237199</v>
+        <v>29.18281867245191</v>
       </c>
       <c r="D21" t="n">
-        <v>1.104441807966636</v>
+        <v>0.9647186827559728</v>
       </c>
       <c r="E21" t="n">
-        <v>12.98530193563792</v>
+        <v>9.929129985498204</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591919607481291</v>
+        <v>0.7521225444737417</v>
       </c>
       <c r="G21" t="n">
-        <v>20.84403750898927</v>
+        <v>17.55367494136427</v>
       </c>
       <c r="H21" t="n">
-        <v>39.26149595058547</v>
+        <v>38.73727993310088</v>
       </c>
       <c r="I21" t="n">
-        <v>1.482715975751103</v>
+        <v>1.278655772271279</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744949754675807</v>
+        <v>4.700765902960885</v>
       </c>
       <c r="K21" t="n">
-        <v>18.81786510564567</v>
+        <v>26.08365223757476</v>
       </c>
       <c r="L21" t="n">
-        <v>45.46148462717707</v>
+        <v>44.69093179347443</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95060620519473</v>
+        <v>99.9574027035011</v>
       </c>
     </row>
   </sheetData>
